--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -169,6 +169,36 @@
   </si>
   <si>
     <t>220023</t>
+  </si>
+  <si>
+    <t>220034</t>
+  </si>
+  <si>
+    <t>220035</t>
+  </si>
+  <si>
+    <t>220024</t>
+  </si>
+  <si>
+    <t>220025</t>
+  </si>
+  <si>
+    <t>220026</t>
+  </si>
+  <si>
+    <t>红色图鉴2</t>
+  </si>
+  <si>
+    <t>220027</t>
+  </si>
+  <si>
+    <t>220028</t>
+  </si>
+  <si>
+    <t>220038</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
   </si>
 </sst>
 </file>
@@ -825,7 +855,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -833,8 +863,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1154,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M32"/>
+  <dimension ref="C1:M44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1276,7 +1312,7 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1311,7 +1347,7 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1346,7 +1382,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1381,7 +1417,7 @@
       <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="8" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1416,7 +1452,7 @@
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1451,7 +1487,7 @@
       <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1486,7 +1522,7 @@
       <c r="D14" s="1">
         <v>3</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1521,7 +1557,7 @@
       <c r="D15" s="1">
         <v>3</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1556,7 +1592,7 @@
       <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1591,7 +1627,7 @@
       <c r="D17" s="1">
         <v>3</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="9" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1626,7 +1662,7 @@
       <c r="D18" s="1">
         <v>3</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1808,7 +1844,7 @@
       <c r="D24" s="1">
         <v>4</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="8" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -1843,7 +1879,7 @@
       <c r="D25" s="1">
         <v>4</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -1878,7 +1914,7 @@
       <c r="D26" s="1">
         <v>4</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -1913,7 +1949,7 @@
       <c r="D27" s="1">
         <v>4</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="9" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -1948,7 +1984,7 @@
       <c r="D28" s="1">
         <v>4</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -2107,6 +2143,382 @@
         <v>1</v>
       </c>
       <c r="L32" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C34" s="1">
+        <v>25</v>
+      </c>
+      <c r="D34" s="1">
+        <v>5</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="1">
+        <v>20</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M34" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="C35" s="1">
+        <v>26</v>
+      </c>
+      <c r="D35" s="1">
+        <v>5</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="1">
+        <v>20</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M35" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
+        <v>27</v>
+      </c>
+      <c r="D36" s="1">
+        <v>5</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>50</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M36" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C37" s="1">
+        <v>28</v>
+      </c>
+      <c r="D37" s="1">
+        <v>5</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1">
+        <v>50</v>
+      </c>
+      <c r="I37" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J37" s="1">
+        <v>10</v>
+      </c>
+      <c r="K37" s="1">
+        <v>50</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M37" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="1">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1">
+        <v>5</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4</v>
+      </c>
+      <c r="H38" s="1">
+        <v>50</v>
+      </c>
+      <c r="I38" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J38" s="1">
+        <v>10</v>
+      </c>
+      <c r="K38" s="1">
+        <v>20</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="C39" s="1">
+        <v>30</v>
+      </c>
+      <c r="D39" s="1">
+        <v>5</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="1">
+        <v>50</v>
+      </c>
+      <c r="I39" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J39" s="1">
+        <v>10</v>
+      </c>
+      <c r="K39" s="1">
+        <v>10</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="1">
+        <v>31</v>
+      </c>
+      <c r="D40" s="1">
+        <v>5</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="1">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>50</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="1">
+        <v>32</v>
+      </c>
+      <c r="D41" s="1">
+        <v>5</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>50</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>33</v>
+      </c>
+      <c r="D42" s="1">
+        <v>5</v>
+      </c>
+      <c r="E42" s="4">
+        <v>180017</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J42" s="1">
+        <v>100</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:12">
+      <c r="C43" s="1">
+        <v>34</v>
+      </c>
+      <c r="D43" s="1">
+        <v>5</v>
+      </c>
+      <c r="E43" s="4">
+        <v>180018</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J43" s="1">
+        <v>100</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="C44" s="1">
+        <v>35</v>
+      </c>
+      <c r="D44" s="3">
+        <v>5</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G44" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J44" s="1">
+        <v>100</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>32</v>
       </c>
     </row>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -855,7 +855,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -865,12 +865,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1312,7 +1310,7 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1347,7 +1345,7 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1382,7 +1380,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1417,7 +1415,7 @@
       <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1452,7 +1450,7 @@
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1487,7 +1485,7 @@
       <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1522,7 +1520,7 @@
       <c r="D14" s="1">
         <v>3</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1557,7 +1555,7 @@
       <c r="D15" s="1">
         <v>3</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1592,7 +1590,7 @@
       <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1627,7 +1625,7 @@
       <c r="D17" s="1">
         <v>3</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1662,7 +1660,7 @@
       <c r="D18" s="1">
         <v>3</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1844,7 +1842,7 @@
       <c r="D24" s="1">
         <v>4</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -1879,7 +1877,7 @@
       <c r="D25" s="1">
         <v>4</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -1914,7 +1912,7 @@
       <c r="D26" s="1">
         <v>4</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -1949,7 +1947,7 @@
       <c r="D27" s="1">
         <v>4</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -1984,7 +1982,7 @@
       <c r="D28" s="1">
         <v>4</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -2153,7 +2151,7 @@
       <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2188,7 +2186,7 @@
       <c r="D35" s="1">
         <v>5</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2223,7 +2221,7 @@
       <c r="D36" s="1">
         <v>5</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -2258,7 +2256,7 @@
       <c r="D37" s="1">
         <v>5</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -2293,7 +2291,7 @@
       <c r="D38" s="1">
         <v>5</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="10" t="s">
         <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -2328,7 +2326,7 @@
       <c r="D39" s="1">
         <v>5</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="9" t="s">
         <v>40</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -2363,7 +2361,7 @@
       <c r="D40" s="1">
         <v>5</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="9" t="s">
         <v>42</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -2398,7 +2396,7 @@
       <c r="D41" s="1">
         <v>5</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -2497,7 +2495,7 @@
       <c r="D44" s="3">
         <v>5</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>44</v>
       </c>
       <c r="F44" s="1" t="s">

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
   <si>
     <t>#</t>
   </si>
@@ -199,6 +199,15 @@
   </si>
   <si>
     <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>220036</t>
+  </si>
+  <si>
+    <t>等级丹*10</t>
+  </si>
+  <si>
+    <t>每百层大概2.5个</t>
   </si>
 </sst>
 </file>
@@ -858,13 +867,13 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -1188,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M44"/>
+  <dimension ref="C1:M45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1217,89 +1226,89 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1765,7 +1774,7 @@
       <c r="D21" s="1">
         <v>3</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>180017</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -1797,7 +1806,7 @@
       <c r="D22" s="1">
         <v>3</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>180018</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -1825,7 +1834,7 @@
     <row r="23" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="3"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -2087,7 +2096,7 @@
       <c r="D31" s="1">
         <v>4</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <v>180017</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -2119,7 +2128,7 @@
       <c r="D32" s="1">
         <v>4</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="5">
         <v>180018</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2431,7 +2440,7 @@
       <c r="D42" s="1">
         <v>5</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="5">
         <v>180017</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -2463,7 +2472,7 @@
       <c r="D43" s="1">
         <v>5</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="5">
         <v>180018</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -2492,7 +2501,7 @@
       <c r="C44" s="1">
         <v>35</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="4">
         <v>5</v>
       </c>
       <c r="E44" s="7" t="s">
@@ -2518,6 +2527,38 @@
       </c>
       <c r="L44" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C45" s="1">
+        <v>36</v>
+      </c>
+      <c r="D45" s="2">
+        <v>5</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G45" s="2">
+        <v>12</v>
+      </c>
+      <c r="H45" s="2">
+        <v>90</v>
+      </c>
+      <c r="I45" s="2">
+        <v>99</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>5</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -171,10 +171,10 @@
     <t>220023</t>
   </si>
   <si>
-    <t>220034</t>
-  </si>
-  <si>
-    <t>220035</t>
+    <t>220039</t>
+  </si>
+  <si>
+    <t>220040</t>
   </si>
   <si>
     <t>220024</t>
@@ -2160,7 +2160,7 @@
       <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2195,7 +2195,7 @@
       <c r="D35" s="1">
         <v>5</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2546,7 +2546,7 @@
         <v>12</v>
       </c>
       <c r="H45" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I45" s="2">
         <v>99</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>每百层大概2.5个</t>
+  </si>
+  <si>
+    <t>220041</t>
+  </si>
+  <si>
+    <t>改造石</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1203,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M45"/>
+  <dimension ref="C1:M46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2561,6 +2567,38 @@
         <v>48</v>
       </c>
     </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="1">
+        <v>37</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" s="2">
+        <v>12</v>
+      </c>
+      <c r="H46" s="2">
+        <v>80</v>
+      </c>
+      <c r="I46" s="2">
+        <v>99</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
+      </c>
+      <c r="K46" s="2">
+        <v>5</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -2581,7 +2581,7 @@
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2">
         <v>80</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2561,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>48</v>
@@ -2581,10 +2581,10 @@
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H46" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I46" s="2">
         <v>99</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2549,10 +2549,10 @@
         <v>47</v>
       </c>
       <c r="G45" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H45" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I45" s="2">
         <v>99</v>
@@ -2581,10 +2581,10 @@
         <v>50</v>
       </c>
       <c r="G46" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H46" s="2">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I46" s="2">
         <v>99</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2519,11 +2519,11 @@
       <c r="G44" s="1">
         <v>5000</v>
       </c>
-      <c r="H44" s="1">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1">
-        <v>10000</v>
+      <c r="H44" s="2">
+        <v>99</v>
+      </c>
+      <c r="I44" s="2">
+        <v>99</v>
       </c>
       <c r="J44" s="1">
         <v>100</v>
@@ -2555,7 +2555,7 @@
         <v>60</v>
       </c>
       <c r="I45" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -2587,7 +2587,7 @@
         <v>70</v>
       </c>
       <c r="I46" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J46" s="2">
         <v>1</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="52">
   <si>
     <t>#</t>
   </si>
@@ -117,58 +117,61 @@
     <t>2000</t>
   </si>
   <si>
+    <t>龙城图鉴</t>
+  </si>
+  <si>
+    <t>每百层大概5个</t>
+  </si>
+  <si>
+    <t>220017</t>
+  </si>
+  <si>
+    <t>220018</t>
+  </si>
+  <si>
+    <t>220019</t>
+  </si>
+  <si>
+    <t>220020</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>橙色图鉴</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>红色图鉴</t>
+  </si>
+  <si>
+    <t>每百层大概2个</t>
+  </si>
+  <si>
+    <t>一期时装</t>
+  </si>
+  <si>
+    <t>二期时装</t>
+  </si>
+  <si>
+    <t>分解机</t>
+  </si>
+  <si>
+    <t>百层的整数倍，大概率掉落</t>
+  </si>
+  <si>
+    <t>摄魂瓶</t>
+  </si>
+  <si>
+    <t>220022</t>
+  </si>
+  <si>
+    <t>220023</t>
+  </si>
+  <si>
     <t>沙城图鉴</t>
-  </si>
-  <si>
-    <t>每百层大概5个</t>
-  </si>
-  <si>
-    <t>220017</t>
-  </si>
-  <si>
-    <t>220018</t>
-  </si>
-  <si>
-    <t>220019</t>
-  </si>
-  <si>
-    <t>220020</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>橙色图鉴</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>红色图鉴</t>
-  </si>
-  <si>
-    <t>每百层大概2个</t>
-  </si>
-  <si>
-    <t>一期时装</t>
-  </si>
-  <si>
-    <t>二期时装</t>
-  </si>
-  <si>
-    <t>分解机</t>
-  </si>
-  <si>
-    <t>百层的整数倍，大概率掉落</t>
-  </si>
-  <si>
-    <t>摄魂瓶</t>
-  </si>
-  <si>
-    <t>220022</t>
-  </si>
-  <si>
-    <t>220023</t>
   </si>
   <si>
     <t>220039</t>
@@ -1966,7 +1969,7 @@
         <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G27" s="1">
         <v>10</v>
@@ -2167,7 +2170,7 @@
         <v>5</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>13</v>
@@ -2202,7 +2205,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>16</v>
@@ -2237,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>25</v>
@@ -2272,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>18</v>
@@ -2342,10 +2345,10 @@
         <v>5</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -2377,7 +2380,7 @@
         <v>5</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>29</v>
@@ -2412,7 +2415,7 @@
         <v>5</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>30</v>
@@ -2511,10 +2514,10 @@
         <v>5</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G44" s="1">
         <v>5000</v>
@@ -2543,10 +2546,10 @@
         <v>5</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" s="2">
         <v>6</v>
@@ -2564,7 +2567,7 @@
         <v>6</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -2575,10 +2578,10 @@
         <v>5</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G46" s="2">
         <v>8</v>
@@ -2596,7 +2599,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="52">
   <si>
     <t>#</t>
   </si>
@@ -1206,7 +1206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M46"/>
+  <dimension ref="C1:M60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2602,6 +2602,448 @@
         <v>49</v>
       </c>
     </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="1">
+        <v>38</v>
+      </c>
+      <c r="D48" s="1">
+        <v>6</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="1">
+        <v>20</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M48" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:13">
+      <c r="C49" s="1">
+        <v>39</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="1">
+        <v>20</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M49" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:13">
+      <c r="C50" s="1">
+        <v>40</v>
+      </c>
+      <c r="D50" s="1">
+        <v>6</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="1">
+        <v>10</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>50</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:13">
+      <c r="C51" s="1">
+        <v>41</v>
+      </c>
+      <c r="D51" s="1">
+        <v>6</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="1">
+        <v>10</v>
+      </c>
+      <c r="H51" s="1">
+        <v>50</v>
+      </c>
+      <c r="I51" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J51" s="1">
+        <v>10</v>
+      </c>
+      <c r="K51" s="1">
+        <v>50</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:13">
+      <c r="C52" s="1">
+        <v>42</v>
+      </c>
+      <c r="D52" s="1">
+        <v>6</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="1">
+        <v>4</v>
+      </c>
+      <c r="H52" s="1">
+        <v>50</v>
+      </c>
+      <c r="I52" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J52" s="1">
+        <v>10</v>
+      </c>
+      <c r="K52" s="1">
+        <v>20</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:13">
+      <c r="C53" s="1">
+        <v>43</v>
+      </c>
+      <c r="D53" s="1">
+        <v>6</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2</v>
+      </c>
+      <c r="H53" s="1">
+        <v>50</v>
+      </c>
+      <c r="I53" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J53" s="1">
+        <v>10</v>
+      </c>
+      <c r="K53" s="1">
+        <v>10</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:13">
+      <c r="C54" s="1">
+        <v>44</v>
+      </c>
+      <c r="D54" s="1">
+        <v>6</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" s="1">
+        <v>10</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>50</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M54" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:13">
+      <c r="C55" s="1">
+        <v>45</v>
+      </c>
+      <c r="D55" s="1">
+        <v>6</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G55" s="1">
+        <v>10</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+      <c r="K55" s="1">
+        <v>50</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:12">
+      <c r="C56" s="1">
+        <v>46</v>
+      </c>
+      <c r="D56" s="1">
+        <v>6</v>
+      </c>
+      <c r="E56" s="5">
+        <v>180017</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J56" s="1">
+        <v>100</v>
+      </c>
+      <c r="K56" s="1">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:12">
+      <c r="C57" s="1">
+        <v>47</v>
+      </c>
+      <c r="D57" s="1">
+        <v>6</v>
+      </c>
+      <c r="E57" s="5">
+        <v>180018</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J57" s="1">
+        <v>100</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:12">
+      <c r="C58" s="1">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1">
+        <v>6</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H58" s="2">
+        <v>99</v>
+      </c>
+      <c r="I58" s="2">
+        <v>99</v>
+      </c>
+      <c r="J58" s="1">
+        <v>100</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:13">
+      <c r="C59" s="1">
+        <v>49</v>
+      </c>
+      <c r="D59" s="1">
+        <v>6</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G59" s="2">
+        <v>6</v>
+      </c>
+      <c r="H59" s="2">
+        <v>60</v>
+      </c>
+      <c r="I59" s="2">
+        <v>98</v>
+      </c>
+      <c r="J59" s="2">
+        <v>1</v>
+      </c>
+      <c r="K59" s="2">
+        <v>6</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" customHeight="1" spans="3:13">
+      <c r="C60" s="1">
+        <v>50</v>
+      </c>
+      <c r="D60" s="1">
+        <v>6</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G60" s="2">
+        <v>8</v>
+      </c>
+      <c r="H60" s="2">
+        <v>70</v>
+      </c>
+      <c r="I60" s="2">
+        <v>98</v>
+      </c>
+      <c r="J60" s="2">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2">
+        <v>5</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M60" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -217,6 +217,18 @@
   </si>
   <si>
     <t>改造石</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>金色精华</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1218,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M60"/>
+  <dimension ref="C1:M63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2995,7 +3007,7 @@
         <v>6</v>
       </c>
       <c r="H59" s="2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="I59" s="2">
         <v>98</v>
@@ -3004,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>49</v>
@@ -3043,6 +3055,75 @@
         <v>49</v>
       </c>
       <c r="M60" s="2"/>
+    </row>
+    <row r="61" customHeight="1" spans="3:13">
+      <c r="C61" s="1">
+        <v>51</v>
+      </c>
+      <c r="D61" s="1">
+        <v>6</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="2">
+        <v>20</v>
+      </c>
+      <c r="H61" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" s="2">
+        <v>50</v>
+      </c>
+      <c r="J61" s="2">
+        <v>1</v>
+      </c>
+      <c r="K61" s="2">
+        <v>10</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="3:13">
+      <c r="C62" s="1">
+        <v>52</v>
+      </c>
+      <c r="D62" s="1">
+        <v>6</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G62" s="2">
+        <v>8</v>
+      </c>
+      <c r="H62" s="2">
+        <v>51</v>
+      </c>
+      <c r="I62" s="2">
+        <v>99</v>
+      </c>
+      <c r="J62" s="2">
+        <v>1</v>
+      </c>
+      <c r="K62" s="2">
+        <v>10</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="5:5">
+      <c r="E63" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2576,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>49</v>
@@ -3004,10 +3004,10 @@
         <v>48</v>
       </c>
       <c r="G59" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H59" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I59" s="2">
         <v>98</v>
@@ -3016,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>49</v>
@@ -3070,13 +3070,13 @@
         <v>53</v>
       </c>
       <c r="G61" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H61" s="2">
         <v>20</v>
       </c>
       <c r="I61" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J61" s="2">
         <v>1</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -3109,7 +3109,7 @@
         <v>51</v>
       </c>
       <c r="I62" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J62" s="2">
         <v>1</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -93,6 +93,9 @@
     <t>Max</t>
   </si>
   <si>
+    <t>Number</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -229,6 +232,12 @@
   </si>
   <si>
     <t>暗金精华</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
+    <t>混沌精华</t>
   </si>
 </sst>
 </file>
@@ -1218,35 +1227,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M63"/>
+  <dimension ref="C1:N78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
     <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="11" width="11.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="9" max="12" width="11.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="23.125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="12:13">
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" customHeight="1" spans="13:14">
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="12:13">
-      <c r="L2" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
+    </row>
+    <row r="2" customHeight="1" spans="13:14">
       <c r="M2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1274,8 +1283,11 @@
       <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1303,37 +1315,43 @@
       <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1341,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
         <v>20</v>
@@ -1361,14 +1379,17 @@
       <c r="K6" s="1">
         <v>1000</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1376,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>20</v>
@@ -1396,14 +1417,17 @@
       <c r="K7" s="1">
         <v>1000</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M7" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1411,10 +1435,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1">
         <v>60</v>
@@ -1431,14 +1455,17 @@
       <c r="K8" s="1">
         <v>10</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>4</v>
       </c>
@@ -1446,10 +1473,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="1">
         <v>20</v>
@@ -1466,14 +1493,17 @@
       <c r="K10" s="1">
         <v>1000</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>5</v>
       </c>
@@ -1481,10 +1511,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>20</v>
@@ -1501,14 +1531,17 @@
       <c r="K11" s="1">
         <v>1000</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>6</v>
       </c>
@@ -1516,10 +1549,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
         <v>40</v>
@@ -1536,14 +1569,17 @@
       <c r="K12" s="1">
         <v>10</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>7</v>
       </c>
@@ -1551,10 +1587,10 @@
         <v>3</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
         <v>20</v>
@@ -1571,14 +1607,17 @@
       <c r="K14" s="1">
         <v>1000</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C15" s="1">
         <v>8</v>
       </c>
@@ -1586,10 +1625,10 @@
         <v>3</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
         <v>20</v>
@@ -1606,14 +1645,17 @@
       <c r="K15" s="1">
         <v>1000</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="1">
         <v>9</v>
       </c>
@@ -1621,10 +1663,10 @@
         <v>3</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1">
         <v>10</v>
@@ -1641,14 +1683,17 @@
       <c r="K16" s="1">
         <v>50</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C17" s="1">
         <v>10</v>
       </c>
@@ -1656,10 +1701,10 @@
         <v>3</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1">
         <v>10</v>
@@ -1676,14 +1721,17 @@
       <c r="K17" s="1">
         <v>50</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:13">
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:14">
       <c r="C18" s="1">
         <v>11</v>
       </c>
@@ -1691,10 +1739,10 @@
         <v>3</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="1">
         <v>4</v>
@@ -1711,14 +1759,17 @@
       <c r="K18" s="1">
         <v>20</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="1">
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:13">
+    <row r="19" customHeight="1" spans="3:14">
       <c r="C19" s="1">
         <v>12</v>
       </c>
@@ -1729,7 +1780,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1">
         <v>10</v>
@@ -1746,14 +1797,17 @@
       <c r="K19" s="1">
         <v>50</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:13">
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:14">
       <c r="C20" s="1">
         <v>13</v>
       </c>
@@ -1764,7 +1818,7 @@
         <v>3002</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G20" s="1">
         <v>10</v>
@@ -1781,14 +1835,17 @@
       <c r="K20" s="1">
         <v>50</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:12">
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:13">
       <c r="C21" s="1">
         <v>14</v>
       </c>
@@ -1799,7 +1856,7 @@
         <v>180017</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" s="1">
         <v>50000</v>
@@ -1816,11 +1873,14 @@
       <c r="K21" s="1">
         <v>1</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:12">
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:13">
       <c r="C22" s="1">
         <v>15</v>
       </c>
@@ -1831,7 +1891,7 @@
         <v>180018</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" s="1">
         <v>10000</v>
@@ -1848,11 +1908,14 @@
       <c r="K22" s="1">
         <v>1</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="4"/>
@@ -1864,8 +1927,9 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
         <v>16</v>
       </c>
@@ -1873,10 +1937,10 @@
         <v>4</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="1">
         <v>20</v>
@@ -1893,14 +1957,17 @@
       <c r="K24" s="1">
         <v>1000</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M24" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N24" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C25" s="1">
         <v>17</v>
       </c>
@@ -1908,10 +1975,10 @@
         <v>4</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1">
         <v>20</v>
@@ -1928,14 +1995,17 @@
       <c r="K25" s="1">
         <v>1000</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M25" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N25" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>18</v>
       </c>
@@ -1943,10 +2013,10 @@
         <v>4</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="1">
         <v>10</v>
@@ -1963,14 +2033,17 @@
       <c r="K26" s="1">
         <v>50</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="1">
         <v>19</v>
       </c>
@@ -1978,10 +2051,10 @@
         <v>4</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G27" s="1">
         <v>10</v>
@@ -1998,14 +2071,17 @@
       <c r="K27" s="1">
         <v>50</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:13">
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:14">
       <c r="C28" s="1">
         <v>20</v>
       </c>
@@ -2013,10 +2089,10 @@
         <v>4</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G28" s="1">
         <v>4</v>
@@ -2033,14 +2109,17 @@
       <c r="K28" s="1">
         <v>20</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M28" s="1">
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:13">
+    <row r="29" customHeight="1" spans="3:14">
       <c r="C29" s="1">
         <v>21</v>
       </c>
@@ -2051,7 +2130,7 @@
         <v>3001</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -2068,14 +2147,17 @@
       <c r="K29" s="1">
         <v>50</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:13">
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:14">
       <c r="C30" s="1">
         <v>22</v>
       </c>
@@ -2086,7 +2168,7 @@
         <v>3002</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G30" s="1">
         <v>10</v>
@@ -2103,14 +2185,17 @@
       <c r="K30" s="1">
         <v>50</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M30" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:12">
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:13">
       <c r="C31" s="1">
         <v>23</v>
       </c>
@@ -2121,7 +2206,7 @@
         <v>180017</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G31" s="1">
         <v>50000</v>
@@ -2138,11 +2223,14 @@
       <c r="K31" s="1">
         <v>1</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:12">
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
       <c r="C32" s="1">
         <v>24</v>
       </c>
@@ -2153,7 +2241,7 @@
         <v>180018</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G32" s="1">
         <v>10000</v>
@@ -2170,11 +2258,14 @@
       <c r="K32" s="1">
         <v>1</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C34" s="1">
         <v>25</v>
       </c>
@@ -2182,10 +2273,10 @@
         <v>5</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
         <v>20</v>
@@ -2202,14 +2293,17 @@
       <c r="K34" s="1">
         <v>1000</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M34" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N34" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
       <c r="C35" s="1">
         <v>26</v>
       </c>
@@ -2217,10 +2311,10 @@
         <v>5</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" s="1">
         <v>20</v>
@@ -2237,14 +2331,17 @@
       <c r="K35" s="1">
         <v>1000</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M35" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N35" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C36" s="1">
         <v>27</v>
       </c>
@@ -2252,10 +2349,10 @@
         <v>5</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G36" s="1">
         <v>10</v>
@@ -2272,14 +2369,17 @@
       <c r="K36" s="1">
         <v>50</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M36" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="L36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="1">
         <v>28</v>
       </c>
@@ -2287,10 +2387,10 @@
         <v>5</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G37" s="1">
         <v>10</v>
@@ -2307,14 +2407,17 @@
       <c r="K37" s="1">
         <v>50</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M37" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:14">
       <c r="C38" s="1">
         <v>29</v>
       </c>
@@ -2322,10 +2425,10 @@
         <v>5</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G38" s="1">
         <v>4</v>
@@ -2342,14 +2445,17 @@
       <c r="K38" s="1">
         <v>20</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N38" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:13">
+    <row r="39" customHeight="1" spans="3:14">
       <c r="C39" s="1">
         <v>30</v>
       </c>
@@ -2357,10 +2463,10 @@
         <v>5</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -2377,14 +2483,17 @@
       <c r="K39" s="1">
         <v>10</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M39" s="1">
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:13">
+    <row r="40" customHeight="1" spans="3:14">
       <c r="C40" s="1">
         <v>31</v>
       </c>
@@ -2392,10 +2501,10 @@
         <v>5</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G40" s="1">
         <v>10</v>
@@ -2412,14 +2521,17 @@
       <c r="K40" s="1">
         <v>50</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M40" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:14">
       <c r="C41" s="1">
         <v>32</v>
       </c>
@@ -2427,10 +2539,10 @@
         <v>5</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41" s="1">
         <v>10</v>
@@ -2447,14 +2559,17 @@
       <c r="K41" s="1">
         <v>50</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M41" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:12">
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N41" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="1">
         <v>33</v>
       </c>
@@ -2465,7 +2580,7 @@
         <v>180017</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G42" s="1">
         <v>50000</v>
@@ -2482,11 +2597,14 @@
       <c r="K42" s="1">
         <v>1</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:12">
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
       <c r="C43" s="1">
         <v>34</v>
       </c>
@@ -2497,7 +2615,7 @@
         <v>180018</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G43" s="1">
         <v>5000</v>
@@ -2514,11 +2632,14 @@
       <c r="K43" s="1">
         <v>1</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
       <c r="C44" s="1">
         <v>35</v>
       </c>
@@ -2526,10 +2647,10 @@
         <v>5</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G44" s="1">
         <v>5000</v>
@@ -2546,11 +2667,14 @@
       <c r="K44" s="1">
         <v>1</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="1">
         <v>36</v>
       </c>
@@ -2558,10 +2682,10 @@
         <v>5</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G45" s="2">
         <v>6</v>
@@ -2578,11 +2702,14 @@
       <c r="K45" s="2">
         <v>5</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="1">
         <v>37</v>
       </c>
@@ -2590,10 +2717,10 @@
         <v>5</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G46" s="2">
         <v>8</v>
@@ -2610,11 +2737,14 @@
       <c r="K46" s="2">
         <v>5</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:14">
       <c r="C48" s="1">
         <v>38</v>
       </c>
@@ -2622,10 +2752,10 @@
         <v>6</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48" s="1">
         <v>20</v>
@@ -2642,14 +2772,17 @@
       <c r="K48" s="1">
         <v>1000</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M48" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:13">
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N48" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:14">
       <c r="C49" s="1">
         <v>39</v>
       </c>
@@ -2657,10 +2790,10 @@
         <v>6</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" s="1">
         <v>20</v>
@@ -2677,14 +2810,17 @@
       <c r="K49" s="1">
         <v>1000</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M49" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:13">
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N49" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:14">
       <c r="C50" s="1">
         <v>40</v>
       </c>
@@ -2692,10 +2828,10 @@
         <v>6</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G50" s="1">
         <v>10</v>
@@ -2712,14 +2848,17 @@
       <c r="K50" s="1">
         <v>50</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M50" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:13">
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N50" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:14">
       <c r="C51" s="1">
         <v>41</v>
       </c>
@@ -2727,10 +2866,10 @@
         <v>6</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G51" s="1">
         <v>10</v>
@@ -2747,14 +2886,17 @@
       <c r="K51" s="1">
         <v>50</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M51" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:13">
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
       <c r="C52" s="1">
         <v>42</v>
       </c>
@@ -2762,10 +2904,10 @@
         <v>6</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G52" s="1">
         <v>4</v>
@@ -2782,14 +2924,17 @@
       <c r="K52" s="1">
         <v>20</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M52" s="1">
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N52" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:13">
+    <row r="53" customHeight="1" spans="3:14">
       <c r="C53" s="1">
         <v>43</v>
       </c>
@@ -2797,10 +2942,10 @@
         <v>6</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G53" s="1">
         <v>2</v>
@@ -2817,14 +2962,17 @@
       <c r="K53" s="1">
         <v>10</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53" s="1">
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N53" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:13">
+    <row r="54" customHeight="1" spans="3:14">
       <c r="C54" s="1">
         <v>44</v>
       </c>
@@ -2832,10 +2980,10 @@
         <v>6</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G54" s="1">
         <v>10</v>
@@ -2852,14 +3000,17 @@
       <c r="K54" s="1">
         <v>50</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M54" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:13">
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N54" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:14">
       <c r="C55" s="1">
         <v>45</v>
       </c>
@@ -2867,10 +3018,10 @@
         <v>6</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G55" s="1">
         <v>10</v>
@@ -2887,14 +3038,17 @@
       <c r="K55" s="1">
         <v>50</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M55" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:12">
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
         <v>46</v>
       </c>
@@ -2905,7 +3059,7 @@
         <v>180017</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G56" s="1">
         <v>50000</v>
@@ -2922,11 +3076,14 @@
       <c r="K56" s="1">
         <v>1</v>
       </c>
-      <c r="L56" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:12">
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
         <v>47</v>
       </c>
@@ -2937,7 +3094,7 @@
         <v>180018</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G57" s="1">
         <v>5000</v>
@@ -2954,11 +3111,14 @@
       <c r="K57" s="1">
         <v>1</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:12">
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
         <v>48</v>
       </c>
@@ -2966,10 +3126,10 @@
         <v>6</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G58" s="1">
         <v>5000</v>
@@ -2986,11 +3146,14 @@
       <c r="K58" s="1">
         <v>1</v>
       </c>
-      <c r="L58" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:13">
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:14">
       <c r="C59" s="1">
         <v>49</v>
       </c>
@@ -2998,10 +3161,10 @@
         <v>6</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G59" s="2">
         <v>3</v>
@@ -3018,12 +3181,15 @@
       <c r="K59" s="2">
         <v>5</v>
       </c>
-      <c r="L59" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M59" s="2"/>
-    </row>
-    <row r="60" customHeight="1" spans="3:13">
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N59" s="2"/>
+    </row>
+    <row r="60" customHeight="1" spans="3:14">
       <c r="C60" s="1">
         <v>50</v>
       </c>
@@ -3031,10 +3197,10 @@
         <v>6</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G60" s="2">
         <v>8</v>
@@ -3051,12 +3217,15 @@
       <c r="K60" s="2">
         <v>5</v>
       </c>
-      <c r="L60" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M60" s="2"/>
-    </row>
-    <row r="61" customHeight="1" spans="3:13">
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N60" s="2"/>
+    </row>
+    <row r="61" customHeight="1" spans="3:14">
       <c r="C61" s="1">
         <v>51</v>
       </c>
@@ -3064,10 +3233,10 @@
         <v>6</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61" s="2">
         <v>10</v>
@@ -3084,12 +3253,15 @@
       <c r="K61" s="2">
         <v>10</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="3:13">
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="3:14">
       <c r="C62" s="1">
         <v>52</v>
       </c>
@@ -3097,10 +3269,10 @@
         <v>6</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G62" s="2">
         <v>8</v>
@@ -3117,13 +3289,569 @@
       <c r="K62" s="2">
         <v>10</v>
       </c>
-      <c r="L62" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M62" s="2"/>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N62" s="2"/>
     </row>
     <row r="63" customHeight="1" spans="5:5">
       <c r="E63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="3:14">
+      <c r="C64" s="1">
+        <v>60</v>
+      </c>
+      <c r="D64" s="1">
+        <v>7</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="1">
+        <v>20</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:14">
+      <c r="C65" s="1">
+        <v>61</v>
+      </c>
+      <c r="D65" s="1">
+        <v>7</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="1">
+        <v>20</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N65" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:14">
+      <c r="C66" s="1">
+        <v>62</v>
+      </c>
+      <c r="D66" s="1">
+        <v>7</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="1">
+        <v>10</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
+        <v>50</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N66" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:14">
+      <c r="C67" s="1">
+        <v>63</v>
+      </c>
+      <c r="D67" s="1">
+        <v>7</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="1">
+        <v>10</v>
+      </c>
+      <c r="H67" s="1">
+        <v>50</v>
+      </c>
+      <c r="I67" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J67" s="1">
+        <v>10</v>
+      </c>
+      <c r="K67" s="1">
+        <v>50</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N67" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:14">
+      <c r="C68" s="1">
+        <v>64</v>
+      </c>
+      <c r="D68" s="1">
+        <v>7</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4</v>
+      </c>
+      <c r="H68" s="1">
+        <v>50</v>
+      </c>
+      <c r="I68" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J68" s="1">
+        <v>10</v>
+      </c>
+      <c r="K68" s="1">
+        <v>20</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:14">
+      <c r="C69" s="1">
+        <v>65</v>
+      </c>
+      <c r="D69" s="1">
+        <v>7</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2</v>
+      </c>
+      <c r="H69" s="1">
+        <v>50</v>
+      </c>
+      <c r="I69" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J69" s="1">
+        <v>10</v>
+      </c>
+      <c r="K69" s="1">
+        <v>10</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:14">
+      <c r="C70" s="1">
+        <v>66</v>
+      </c>
+      <c r="D70" s="1">
+        <v>7</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" s="1">
+        <v>10</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>50</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N70" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:14">
+      <c r="C71" s="1">
+        <v>67</v>
+      </c>
+      <c r="D71" s="1">
+        <v>7</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" s="1">
+        <v>10</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1</v>
+      </c>
+      <c r="K71" s="1">
+        <v>50</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N71" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:13">
+      <c r="C72" s="1">
+        <v>68</v>
+      </c>
+      <c r="D72" s="1">
+        <v>7</v>
+      </c>
+      <c r="E72" s="5">
+        <v>180017</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G72" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J72" s="1">
+        <v>100</v>
+      </c>
+      <c r="K72" s="1">
+        <v>1</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:13">
+      <c r="C73" s="1">
+        <v>69</v>
+      </c>
+      <c r="D73" s="1">
+        <v>7</v>
+      </c>
+      <c r="E73" s="5">
+        <v>180018</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G73" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1</v>
+      </c>
+      <c r="I73" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J73" s="1">
+        <v>100</v>
+      </c>
+      <c r="K73" s="1">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:13">
+      <c r="C74" s="1">
+        <v>70</v>
+      </c>
+      <c r="D74" s="1">
+        <v>7</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G74" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H74" s="2">
+        <v>99</v>
+      </c>
+      <c r="I74" s="2">
+        <v>99</v>
+      </c>
+      <c r="J74" s="1">
+        <v>100</v>
+      </c>
+      <c r="K74" s="1">
+        <v>1</v>
+      </c>
+      <c r="L74" s="1">
+        <v>1</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:14">
+      <c r="C75" s="1">
+        <v>71</v>
+      </c>
+      <c r="D75" s="1">
+        <v>7</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" s="2">
+        <v>3</v>
+      </c>
+      <c r="H75" s="2">
+        <v>10</v>
+      </c>
+      <c r="I75" s="2">
+        <v>98</v>
+      </c>
+      <c r="J75" s="2">
+        <v>1</v>
+      </c>
+      <c r="K75" s="2">
+        <v>5</v>
+      </c>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N75" s="2"/>
+    </row>
+    <row r="76" customHeight="1" spans="3:14">
+      <c r="C76" s="1">
+        <v>72</v>
+      </c>
+      <c r="D76" s="1">
+        <v>7</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="2">
+        <v>8</v>
+      </c>
+      <c r="H76" s="2">
+        <v>10</v>
+      </c>
+      <c r="I76" s="2">
+        <v>98</v>
+      </c>
+      <c r="J76" s="2">
+        <v>1</v>
+      </c>
+      <c r="K76" s="2">
+        <v>15</v>
+      </c>
+      <c r="L76" s="1">
+        <v>1</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N76" s="2"/>
+    </row>
+    <row r="77" customHeight="1" spans="3:14">
+      <c r="C77" s="1">
+        <v>73</v>
+      </c>
+      <c r="D77" s="1">
+        <v>7</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" s="2">
+        <v>10</v>
+      </c>
+      <c r="H77" s="2">
+        <v>70</v>
+      </c>
+      <c r="I77" s="2">
+        <v>100</v>
+      </c>
+      <c r="J77" s="2">
+        <v>1</v>
+      </c>
+      <c r="K77" s="2">
+        <v>5</v>
+      </c>
+      <c r="L77" s="1">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N77" s="2"/>
+    </row>
+    <row r="78" customHeight="1" spans="3:14">
+      <c r="C78" s="1">
+        <v>74</v>
+      </c>
+      <c r="D78" s="1">
+        <v>7</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G78" s="2">
+        <v>8</v>
+      </c>
+      <c r="H78" s="2">
+        <v>95</v>
+      </c>
+      <c r="I78" s="2">
+        <v>100</v>
+      </c>
+      <c r="J78" s="2">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2">
+        <v>2</v>
+      </c>
+      <c r="L78" s="1">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N78" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>混沌精华</t>
+  </si>
+  <si>
+    <t>随机宝石</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N78"/>
+  <dimension ref="C1:N79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3329,7 +3332,7 @@
         <v>1000</v>
       </c>
       <c r="L64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>15</v>
@@ -3367,7 +3370,7 @@
         <v>1000</v>
       </c>
       <c r="L65" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>15</v>
@@ -3405,7 +3408,7 @@
         <v>50</v>
       </c>
       <c r="L66" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>20</v>
@@ -3443,7 +3446,7 @@
         <v>50</v>
       </c>
       <c r="L67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>20</v>
@@ -3481,7 +3484,7 @@
         <v>20</v>
       </c>
       <c r="L68" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>29</v>
@@ -3519,7 +3522,7 @@
         <v>10</v>
       </c>
       <c r="L69" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>29</v>
@@ -3557,7 +3560,7 @@
         <v>50</v>
       </c>
       <c r="L70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>20</v>
@@ -3595,7 +3598,7 @@
         <v>50</v>
       </c>
       <c r="L71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>20</v>
@@ -3852,6 +3855,35 @@
         <v>50</v>
       </c>
       <c r="N78" s="2"/>
+    </row>
+    <row r="79" customHeight="1" spans="3:12">
+      <c r="C79" s="1">
+        <v>75</v>
+      </c>
+      <c r="D79" s="1">
+        <v>7</v>
+      </c>
+      <c r="E79" s="1">
+        <v>601</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G79" s="1">
+        <v>8</v>
+      </c>
+      <c r="H79" s="1">
+        <v>20</v>
+      </c>
+      <c r="I79" s="1">
+        <v>100</v>
+      </c>
+      <c r="K79" s="1">
+        <v>20</v>
+      </c>
+      <c r="L79" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -3870,13 +3870,16 @@
         <v>59</v>
       </c>
       <c r="G79" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H79" s="1">
         <v>20</v>
       </c>
       <c r="I79" s="1">
         <v>100</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1</v>
       </c>
       <c r="K79" s="1">
         <v>20</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -241,6 +241,18 @@
   </si>
   <si>
     <t>随机宝石</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>宠物口粮</t>
+  </si>
+  <si>
+    <t>1016</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N79"/>
+  <dimension ref="C1:N97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1242,7 +1254,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="13:14">
+    <row r="1" customHeight="1" spans="3:14">
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1250,7 +1262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="13:14">
+    <row r="2" customHeight="1" spans="3:14">
       <c r="M2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1290,7 +1302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1322,7 +1334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1354,7 +1366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="6" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1392,7 +1404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+    <row r="7" s="1" customFormat="1" ht="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1430,7 +1442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="8" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1468,7 +1480,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="9" hidden="1" customHeight="1"/>
+    <row r="10" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>4</v>
       </c>
@@ -1506,7 +1519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+    <row r="11" s="1" customFormat="1" ht="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>5</v>
       </c>
@@ -1544,7 +1557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="12" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>6</v>
       </c>
@@ -1582,7 +1595,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="13" hidden="1" customHeight="1"/>
+    <row r="14" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>7</v>
       </c>
@@ -1620,7 +1634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+    <row r="15" s="1" customFormat="1" ht="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C15" s="1">
         <v>8</v>
       </c>
@@ -1658,7 +1672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="16" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C16" s="1">
         <v>9</v>
       </c>
@@ -1696,7 +1710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="17" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C17" s="1">
         <v>10</v>
       </c>
@@ -1734,7 +1748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:14">
+    <row r="18" hidden="1" customHeight="1" spans="3:14">
       <c r="C18" s="1">
         <v>11</v>
       </c>
@@ -1772,7 +1786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:14">
+    <row r="19" hidden="1" customHeight="1" spans="3:14">
       <c r="C19" s="1">
         <v>12</v>
       </c>
@@ -1810,7 +1824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:14">
+    <row r="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C20" s="1">
         <v>13</v>
       </c>
@@ -1848,7 +1862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:13">
+    <row r="21" hidden="1" customHeight="1" spans="3:14">
       <c r="C21" s="1">
         <v>14</v>
       </c>
@@ -1883,7 +1897,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:13">
+    <row r="22" hidden="1" customHeight="1" spans="3:14">
       <c r="C22" s="1">
         <v>15</v>
       </c>
@@ -1918,7 +1932,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:14">
+    <row r="23" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="4"/>
@@ -1932,7 +1946,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="24" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
         <v>16</v>
       </c>
@@ -1970,7 +1984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+    <row r="25" s="1" customFormat="1" ht="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C25" s="1">
         <v>17</v>
       </c>
@@ -2008,7 +2022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="26" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>18</v>
       </c>
@@ -2046,7 +2060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="27" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C27" s="1">
         <v>19</v>
       </c>
@@ -2084,7 +2098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:14">
+    <row r="28" hidden="1" customHeight="1" spans="3:14">
       <c r="C28" s="1">
         <v>20</v>
       </c>
@@ -2122,7 +2136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:14">
+    <row r="29" hidden="1" customHeight="1" spans="3:14">
       <c r="C29" s="1">
         <v>21</v>
       </c>
@@ -2160,7 +2174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:14">
+    <row r="30" hidden="1" customHeight="1" spans="3:14">
       <c r="C30" s="1">
         <v>22</v>
       </c>
@@ -2198,7 +2212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:13">
+    <row r="31" hidden="1" customHeight="1" spans="3:14">
       <c r="C31" s="1">
         <v>23</v>
       </c>
@@ -2233,7 +2247,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:13">
+    <row r="32" hidden="1" customHeight="1" spans="3:14">
       <c r="C32" s="1">
         <v>24</v>
       </c>
@@ -2268,7 +2282,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="33" hidden="1" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C34" s="1">
         <v>25</v>
       </c>
@@ -2306,7 +2321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="3:14">
+    <row r="35" s="1" customFormat="1" ht="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C35" s="1">
         <v>26</v>
       </c>
@@ -2344,7 +2359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="36" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C36" s="1">
         <v>27</v>
       </c>
@@ -2382,7 +2397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="37" s="1" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C37" s="1">
         <v>28</v>
       </c>
@@ -2420,7 +2435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:14">
+    <row r="38" hidden="1" customHeight="1" spans="3:14">
       <c r="C38" s="1">
         <v>29</v>
       </c>
@@ -2458,7 +2473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:14">
+    <row r="39" hidden="1" customHeight="1" spans="3:14">
       <c r="C39" s="1">
         <v>30</v>
       </c>
@@ -2496,7 +2511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:14">
+    <row r="40" hidden="1" customHeight="1" spans="3:14">
       <c r="C40" s="1">
         <v>31</v>
       </c>
@@ -2534,7 +2549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:14">
+    <row r="41" hidden="1" customHeight="1" spans="3:14">
       <c r="C41" s="1">
         <v>32</v>
       </c>
@@ -2572,7 +2587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:13">
+    <row r="42" hidden="1" customHeight="1" spans="3:14">
       <c r="C42" s="1">
         <v>33</v>
       </c>
@@ -2607,7 +2622,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:13">
+    <row r="43" hidden="1" customHeight="1" spans="3:14">
       <c r="C43" s="1">
         <v>34</v>
       </c>
@@ -2642,7 +2657,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="20" customHeight="1" spans="3:13">
+    <row r="44" s="1" customFormat="1" ht="20" hidden="1" customHeight="1" spans="3:14">
       <c r="C44" s="1">
         <v>35</v>
       </c>
@@ -2677,7 +2692,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="45" s="2" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C45" s="1">
         <v>36</v>
       </c>
@@ -2712,7 +2727,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:13">
+    <row r="46" s="2" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C46" s="1">
         <v>37</v>
       </c>
@@ -2747,7 +2762,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:14">
+    <row r="47" hidden="1" customHeight="1"/>
+    <row r="48" hidden="1" customHeight="1" spans="3:14">
       <c r="C48" s="1">
         <v>38</v>
       </c>
@@ -2785,7 +2801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:14">
+    <row r="49" hidden="1" customHeight="1" spans="3:14">
       <c r="C49" s="1">
         <v>39</v>
       </c>
@@ -2823,7 +2839,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:14">
+    <row r="50" hidden="1" customHeight="1" spans="3:14">
       <c r="C50" s="1">
         <v>40</v>
       </c>
@@ -2861,7 +2877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:14">
+    <row r="51" hidden="1" customHeight="1" spans="3:14">
       <c r="C51" s="1">
         <v>41</v>
       </c>
@@ -2899,7 +2915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:14">
+    <row r="52" hidden="1" customHeight="1" spans="3:14">
       <c r="C52" s="1">
         <v>42</v>
       </c>
@@ -2937,7 +2953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:14">
+    <row r="53" hidden="1" customHeight="1" spans="3:14">
       <c r="C53" s="1">
         <v>43</v>
       </c>
@@ -2975,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:14">
+    <row r="54" hidden="1" customHeight="1" spans="3:14">
       <c r="C54" s="1">
         <v>44</v>
       </c>
@@ -3013,7 +3029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:14">
+    <row r="55" hidden="1" customHeight="1" spans="3:14">
       <c r="C55" s="1">
         <v>45</v>
       </c>
@@ -3051,7 +3067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="3:13">
+    <row r="56" hidden="1" customHeight="1" spans="3:14">
       <c r="C56" s="1">
         <v>46</v>
       </c>
@@ -3086,7 +3102,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:13">
+    <row r="57" hidden="1" customHeight="1" spans="3:14">
       <c r="C57" s="1">
         <v>47</v>
       </c>
@@ -3121,7 +3137,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:13">
+    <row r="58" hidden="1" customHeight="1" spans="3:14">
       <c r="C58" s="1">
         <v>48</v>
       </c>
@@ -3156,7 +3172,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:14">
+    <row r="59" hidden="1" customHeight="1" spans="3:14">
       <c r="C59" s="1">
         <v>49</v>
       </c>
@@ -3192,7 +3208,7 @@
       </c>
       <c r="N59" s="2"/>
     </row>
-    <row r="60" customHeight="1" spans="3:14">
+    <row r="60" hidden="1" customHeight="1" spans="3:14">
       <c r="C60" s="1">
         <v>50</v>
       </c>
@@ -3228,7 +3244,7 @@
       </c>
       <c r="N60" s="2"/>
     </row>
-    <row r="61" customHeight="1" spans="3:14">
+    <row r="61" hidden="1" customHeight="1" spans="3:14">
       <c r="C61" s="1">
         <v>51</v>
       </c>
@@ -3264,7 +3280,7 @@
       </c>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" customHeight="1" spans="3:14">
+    <row r="62" hidden="1" customHeight="1" spans="3:14">
       <c r="C62" s="1">
         <v>52</v>
       </c>
@@ -3290,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L62" s="1">
         <v>1</v>
@@ -3300,7 +3316,7 @@
       </c>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" customHeight="1" spans="5:5">
+    <row r="63" customHeight="1" spans="3:14">
       <c r="E63" s="6"/>
     </row>
     <row r="64" customHeight="1" spans="3:14">
@@ -3607,7 +3623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:13">
+    <row r="72" customHeight="1" spans="3:14">
       <c r="C72" s="1">
         <v>68</v>
       </c>
@@ -3642,7 +3658,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="3:13">
+    <row r="73" customHeight="1" spans="3:14">
       <c r="C73" s="1">
         <v>69</v>
       </c>
@@ -3677,7 +3693,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="3:13">
+    <row r="74" customHeight="1" spans="3:14">
       <c r="C74" s="1">
         <v>70</v>
       </c>
@@ -3856,7 +3872,7 @@
       </c>
       <c r="N78" s="2"/>
     </row>
-    <row r="79" customHeight="1" spans="3:12">
+    <row r="79" customHeight="1" spans="3:14">
       <c r="C79" s="1">
         <v>75</v>
       </c>
@@ -3885,6 +3901,626 @@
         <v>20</v>
       </c>
       <c r="L79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:14">
+      <c r="C81" s="1">
+        <v>80</v>
+      </c>
+      <c r="D81" s="1">
+        <v>8</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="1">
+        <v>20</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1</v>
+      </c>
+      <c r="K81" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L81" s="1">
+        <v>5</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N81" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:14">
+      <c r="C82" s="1">
+        <v>81</v>
+      </c>
+      <c r="D82" s="1">
+        <v>8</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" s="1">
+        <v>20</v>
+      </c>
+      <c r="H82" s="1">
+        <v>1</v>
+      </c>
+      <c r="I82" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+      <c r="K82" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L82" s="1">
+        <v>5</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N82" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:14">
+      <c r="C83" s="1">
+        <v>82</v>
+      </c>
+      <c r="D83" s="1">
+        <v>8</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G83" s="1">
+        <v>20</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1</v>
+      </c>
+      <c r="K83" s="1">
+        <v>10</v>
+      </c>
+      <c r="L83" s="1">
+        <v>100</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:14">
+      <c r="C84" s="1">
+        <v>83</v>
+      </c>
+      <c r="D84" s="1">
+        <v>8</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="1">
+        <v>10</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+      <c r="K84" s="1">
+        <v>50</v>
+      </c>
+      <c r="L84" s="1">
+        <v>3</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N84" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:14">
+      <c r="C85" s="1">
+        <v>84</v>
+      </c>
+      <c r="D85" s="1">
+        <v>8</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
+      <c r="H85" s="1">
+        <v>50</v>
+      </c>
+      <c r="I85" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J85" s="1">
+        <v>10</v>
+      </c>
+      <c r="K85" s="1">
+        <v>50</v>
+      </c>
+      <c r="L85" s="1">
+        <v>3</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N85" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:14">
+      <c r="C86" s="1">
+        <v>85</v>
+      </c>
+      <c r="D86" s="1">
+        <v>8</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="1">
+        <v>4</v>
+      </c>
+      <c r="H86" s="1">
+        <v>50</v>
+      </c>
+      <c r="I86" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J86" s="1">
+        <v>10</v>
+      </c>
+      <c r="K86" s="1">
+        <v>20</v>
+      </c>
+      <c r="L86" s="1">
+        <v>2</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N86" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:14">
+      <c r="C87" s="1">
+        <v>86</v>
+      </c>
+      <c r="D87" s="1">
+        <v>8</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G87" s="1">
+        <v>2</v>
+      </c>
+      <c r="H87" s="1">
+        <v>50</v>
+      </c>
+      <c r="I87" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J87" s="1">
+        <v>10</v>
+      </c>
+      <c r="K87" s="1">
+        <v>10</v>
+      </c>
+      <c r="L87" s="1">
+        <v>2</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:14">
+      <c r="C88" s="1">
+        <v>87</v>
+      </c>
+      <c r="D88" s="1">
+        <v>8</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="1">
+        <v>10</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1</v>
+      </c>
+      <c r="K88" s="1">
+        <v>50</v>
+      </c>
+      <c r="L88" s="1">
+        <v>3</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N88" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:14">
+      <c r="C89" s="1">
+        <v>88</v>
+      </c>
+      <c r="D89" s="1">
+        <v>8</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G89" s="1">
+        <v>10</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1</v>
+      </c>
+      <c r="I89" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J89" s="1">
+        <v>1</v>
+      </c>
+      <c r="K89" s="1">
+        <v>50</v>
+      </c>
+      <c r="L89" s="1">
+        <v>3</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N89" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:14">
+      <c r="C90" s="1">
+        <v>89</v>
+      </c>
+      <c r="D90" s="1">
+        <v>8</v>
+      </c>
+      <c r="E90" s="5">
+        <v>180017</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G90" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J90" s="1">
+        <v>100</v>
+      </c>
+      <c r="K90" s="1">
+        <v>1</v>
+      </c>
+      <c r="L90" s="1">
+        <v>1</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:14">
+      <c r="C91" s="1">
+        <v>90</v>
+      </c>
+      <c r="D91" s="1">
+        <v>8</v>
+      </c>
+      <c r="E91" s="5">
+        <v>180018</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G91" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1</v>
+      </c>
+      <c r="I91" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J91" s="1">
+        <v>100</v>
+      </c>
+      <c r="K91" s="1">
+        <v>1</v>
+      </c>
+      <c r="L91" s="1">
+        <v>1</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:14">
+      <c r="C92" s="1">
+        <v>91</v>
+      </c>
+      <c r="D92" s="1">
+        <v>8</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G92" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H92" s="2">
+        <v>99</v>
+      </c>
+      <c r="I92" s="2">
+        <v>99</v>
+      </c>
+      <c r="J92" s="1">
+        <v>100</v>
+      </c>
+      <c r="K92" s="1">
+        <v>1</v>
+      </c>
+      <c r="L92" s="1">
+        <v>2</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:14">
+      <c r="C93" s="1">
+        <v>92</v>
+      </c>
+      <c r="D93" s="1">
+        <v>8</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G93" s="2">
+        <v>3</v>
+      </c>
+      <c r="H93" s="2">
+        <v>10</v>
+      </c>
+      <c r="I93" s="2">
+        <v>98</v>
+      </c>
+      <c r="J93" s="2">
+        <v>1</v>
+      </c>
+      <c r="K93" s="2">
+        <v>5</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N93" s="2"/>
+    </row>
+    <row r="94" customHeight="1" spans="3:14">
+      <c r="C94" s="1">
+        <v>93</v>
+      </c>
+      <c r="D94" s="1">
+        <v>8</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G94" s="2">
+        <v>8</v>
+      </c>
+      <c r="H94" s="2">
+        <v>10</v>
+      </c>
+      <c r="I94" s="2">
+        <v>98</v>
+      </c>
+      <c r="J94" s="2">
+        <v>1</v>
+      </c>
+      <c r="K94" s="2">
+        <v>15</v>
+      </c>
+      <c r="L94" s="1">
+        <v>2</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N94" s="2"/>
+    </row>
+    <row r="95" customHeight="1" spans="3:14">
+      <c r="C95" s="1">
+        <v>94</v>
+      </c>
+      <c r="D95" s="1">
+        <v>8</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G95" s="2">
+        <v>10</v>
+      </c>
+      <c r="H95" s="2">
+        <v>70</v>
+      </c>
+      <c r="I95" s="2">
+        <v>100</v>
+      </c>
+      <c r="J95" s="2">
+        <v>1</v>
+      </c>
+      <c r="K95" s="2">
+        <v>5</v>
+      </c>
+      <c r="L95" s="1">
+        <v>1</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N95" s="2"/>
+    </row>
+    <row r="96" customHeight="1" spans="3:14">
+      <c r="C96" s="1">
+        <v>95</v>
+      </c>
+      <c r="D96" s="1">
+        <v>8</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G96" s="2">
+        <v>8</v>
+      </c>
+      <c r="H96" s="2">
+        <v>95</v>
+      </c>
+      <c r="I96" s="2">
+        <v>100</v>
+      </c>
+      <c r="J96" s="2">
+        <v>1</v>
+      </c>
+      <c r="K96" s="2">
+        <v>2</v>
+      </c>
+      <c r="L96" s="1">
+        <v>1</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N96" s="2"/>
+    </row>
+    <row r="97" customHeight="1" spans="3:12">
+      <c r="C97" s="1">
+        <v>96</v>
+      </c>
+      <c r="D97" s="1">
+        <v>8</v>
+      </c>
+      <c r="E97" s="1">
+        <v>601</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G97" s="1">
+        <v>12</v>
+      </c>
+      <c r="H97" s="1">
+        <v>20</v>
+      </c>
+      <c r="I97" s="1">
+        <v>100</v>
+      </c>
+      <c r="J97" s="1">
+        <v>1</v>
+      </c>
+      <c r="K97" s="1">
+        <v>20</v>
+      </c>
+      <c r="L97" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4398,10 +4398,10 @@
         <v>52</v>
       </c>
       <c r="G94" s="2">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="H94" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I94" s="2">
         <v>98</v>
@@ -4410,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="K94" s="2">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="L94" s="1">
         <v>2</v>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="82">
   <si>
     <t>#</t>
   </si>
@@ -253,6 +253,60 @@
   </si>
   <si>
     <t>不朽精华</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>坐骑兽粮</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>3004</t>
+  </si>
+  <si>
+    <t>三期时装</t>
+  </si>
+  <si>
+    <t>3005</t>
+  </si>
+  <si>
+    <t>四期时装</t>
+  </si>
+  <si>
+    <t>3006</t>
+  </si>
+  <si>
+    <t>五期时装</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>皮肤精华</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>红色魂心</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>永恒精华</t>
+  </si>
+  <si>
+    <t>1019</t>
+  </si>
+  <si>
+    <t>虚无精华</t>
+  </si>
+  <si>
+    <t>随机极宝石</t>
   </si>
 </sst>
 </file>
@@ -909,16 +963,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -1242,7 +1298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N97"/>
+  <dimension ref="C1:N116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1271,98 +1327,98 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1373,7 +1429,7 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1411,7 +1467,7 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1449,7 +1505,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1488,7 +1544,7 @@
       <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1526,7 +1582,7 @@
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1564,7 +1620,7 @@
       <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1603,7 +1659,7 @@
       <c r="D14" s="1">
         <v>3</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1641,7 +1697,7 @@
       <c r="D15" s="1">
         <v>3</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1679,7 +1735,7 @@
       <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1717,7 +1773,7 @@
       <c r="D17" s="1">
         <v>3</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1755,7 +1811,7 @@
       <c r="D18" s="1">
         <v>3</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="10" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1869,7 +1925,7 @@
       <c r="D21" s="1">
         <v>3</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6">
         <v>180017</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -1904,7 +1960,7 @@
       <c r="D22" s="1">
         <v>3</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="6">
         <v>180018</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -1935,7 +1991,7 @@
     <row r="23" customFormat="1" hidden="1" customHeight="1" spans="3:14">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="4"/>
+      <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1953,7 +2009,7 @@
       <c r="D24" s="1">
         <v>4</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -1991,7 +2047,7 @@
       <c r="D25" s="1">
         <v>4</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -2029,7 +2085,7 @@
       <c r="D26" s="1">
         <v>4</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -2067,7 +2123,7 @@
       <c r="D27" s="1">
         <v>4</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -2105,7 +2161,7 @@
       <c r="D28" s="1">
         <v>4</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="10" t="s">
         <v>27</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -2219,7 +2275,7 @@
       <c r="D31" s="1">
         <v>4</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="6">
         <v>180017</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -2254,7 +2310,7 @@
       <c r="D32" s="1">
         <v>4</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="6">
         <v>180018</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2290,7 +2346,7 @@
       <c r="D34" s="1">
         <v>5</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2328,7 +2384,7 @@
       <c r="D35" s="1">
         <v>5</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2366,7 +2422,7 @@
       <c r="D36" s="1">
         <v>5</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="11" t="s">
         <v>40</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -2404,7 +2460,7 @@
       <c r="D37" s="1">
         <v>5</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -2442,7 +2498,7 @@
       <c r="D38" s="1">
         <v>5</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -2480,7 +2536,7 @@
       <c r="D39" s="1">
         <v>5</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -2518,7 +2574,7 @@
       <c r="D40" s="1">
         <v>5</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="11" t="s">
         <v>44</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -2556,7 +2612,7 @@
       <c r="D41" s="1">
         <v>5</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -2594,7 +2650,7 @@
       <c r="D42" s="1">
         <v>5</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="6">
         <v>180017</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -2629,7 +2685,7 @@
       <c r="D43" s="1">
         <v>5</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="6">
         <v>180018</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -2661,10 +2717,10 @@
       <c r="C44" s="1">
         <v>35</v>
       </c>
-      <c r="D44" s="4">
-        <v>5</v>
-      </c>
-      <c r="E44" s="7" t="s">
+      <c r="D44" s="5">
+        <v>5</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>46</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -2699,7 +2755,7 @@
       <c r="D45" s="2">
         <v>5</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="11" t="s">
         <v>48</v>
       </c>
       <c r="F45" s="2" t="s">
@@ -2734,7 +2790,7 @@
       <c r="D46" s="2">
         <v>5</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="9" t="s">
         <v>51</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -2770,7 +2826,7 @@
       <c r="D48" s="1">
         <v>6</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -2808,7 +2864,7 @@
       <c r="D49" s="1">
         <v>6</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -2846,7 +2902,7 @@
       <c r="D50" s="1">
         <v>6</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="11" t="s">
         <v>40</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -2884,7 +2940,7 @@
       <c r="D51" s="1">
         <v>6</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -2922,7 +2978,7 @@
       <c r="D52" s="1">
         <v>6</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -2960,7 +3016,7 @@
       <c r="D53" s="1">
         <v>6</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -2998,7 +3054,7 @@
       <c r="D54" s="1">
         <v>6</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="11" t="s">
         <v>44</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -3036,7 +3092,7 @@
       <c r="D55" s="1">
         <v>6</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -3074,7 +3130,7 @@
       <c r="D56" s="1">
         <v>6</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="6">
         <v>180017</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -3109,7 +3165,7 @@
       <c r="D57" s="1">
         <v>6</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="6">
         <v>180018</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -3144,7 +3200,7 @@
       <c r="D58" s="1">
         <v>6</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="9" t="s">
         <v>46</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -3179,7 +3235,7 @@
       <c r="D59" s="1">
         <v>6</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="11" t="s">
         <v>48</v>
       </c>
       <c r="F59" s="2" t="s">
@@ -3215,7 +3271,7 @@
       <c r="D60" s="1">
         <v>6</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="9" t="s">
         <v>51</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -3251,7 +3307,7 @@
       <c r="D61" s="1">
         <v>6</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -3287,7 +3343,7 @@
       <c r="D62" s="1">
         <v>6</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -3317,7 +3373,7 @@
       <c r="N62" s="2"/>
     </row>
     <row r="63" customHeight="1" spans="3:14">
-      <c r="E63" s="6"/>
+      <c r="E63" s="7"/>
     </row>
     <row r="64" customHeight="1" spans="3:14">
       <c r="C64" s="1">
@@ -3326,7 +3382,7 @@
       <c r="D64" s="1">
         <v>7</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -3364,7 +3420,7 @@
       <c r="D65" s="1">
         <v>7</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -3402,7 +3458,7 @@
       <c r="D66" s="1">
         <v>7</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="11" t="s">
         <v>40</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -3440,7 +3496,7 @@
       <c r="D67" s="1">
         <v>7</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -3478,7 +3534,7 @@
       <c r="D68" s="1">
         <v>7</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -3516,7 +3572,7 @@
       <c r="D69" s="1">
         <v>7</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="E69" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -3554,7 +3610,7 @@
       <c r="D70" s="1">
         <v>7</v>
       </c>
-      <c r="E70" s="9" t="s">
+      <c r="E70" s="11" t="s">
         <v>44</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -3592,7 +3648,7 @@
       <c r="D71" s="1">
         <v>7</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="E71" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -3630,7 +3686,7 @@
       <c r="D72" s="1">
         <v>7</v>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="6">
         <v>180017</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -3665,7 +3721,7 @@
       <c r="D73" s="1">
         <v>7</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="6">
         <v>180018</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -3700,7 +3756,7 @@
       <c r="D74" s="1">
         <v>7</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="9" t="s">
         <v>46</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -3735,7 +3791,7 @@
       <c r="D75" s="1">
         <v>7</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="E75" s="11" t="s">
         <v>48</v>
       </c>
       <c r="F75" s="2" t="s">
@@ -3771,7 +3827,7 @@
       <c r="D76" s="1">
         <v>7</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="9" t="s">
         <v>51</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -3807,7 +3863,7 @@
       <c r="D77" s="1">
         <v>7</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="9" t="s">
         <v>53</v>
       </c>
       <c r="F77" s="1" t="s">
@@ -3843,7 +3899,7 @@
       <c r="D78" s="1">
         <v>7</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F78" s="1" t="s">
@@ -3911,7 +3967,7 @@
       <c r="D81" s="1">
         <v>8</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -3949,7 +4005,7 @@
       <c r="D82" s="1">
         <v>8</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -3987,7 +4043,7 @@
       <c r="D83" s="1">
         <v>8</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="9" t="s">
         <v>60</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -4022,7 +4078,7 @@
       <c r="D84" s="1">
         <v>8</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="E84" s="11" t="s">
         <v>40</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -4060,7 +4116,7 @@
       <c r="D85" s="1">
         <v>8</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -4098,7 +4154,7 @@
       <c r="D86" s="1">
         <v>8</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -4136,7 +4192,7 @@
       <c r="D87" s="1">
         <v>8</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E87" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F87" s="1" t="s">
@@ -4174,7 +4230,7 @@
       <c r="D88" s="1">
         <v>8</v>
       </c>
-      <c r="E88" s="9" t="s">
+      <c r="E88" s="11" t="s">
         <v>44</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -4212,7 +4268,7 @@
       <c r="D89" s="1">
         <v>8</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F89" s="1" t="s">
@@ -4250,7 +4306,7 @@
       <c r="D90" s="1">
         <v>8</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="6">
         <v>180017</v>
       </c>
       <c r="F90" s="1" t="s">
@@ -4285,7 +4341,7 @@
       <c r="D91" s="1">
         <v>8</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="6">
         <v>180018</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -4320,7 +4376,7 @@
       <c r="D92" s="1">
         <v>8</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="9" t="s">
         <v>46</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -4355,7 +4411,7 @@
       <c r="D93" s="1">
         <v>8</v>
       </c>
-      <c r="E93" s="9" t="s">
+      <c r="E93" s="11" t="s">
         <v>48</v>
       </c>
       <c r="F93" s="2" t="s">
@@ -4391,7 +4447,7 @@
       <c r="D94" s="1">
         <v>8</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="9" t="s">
         <v>51</v>
       </c>
       <c r="F94" s="1" t="s">
@@ -4427,7 +4483,7 @@
       <c r="D95" s="1">
         <v>8</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="9" t="s">
         <v>62</v>
       </c>
       <c r="F95" s="1" t="s">
@@ -4463,7 +4519,7 @@
       <c r="D96" s="1">
         <v>8</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F96" s="1" t="s">
@@ -4492,7 +4548,7 @@
       </c>
       <c r="N96" s="2"/>
     </row>
-    <row r="97" customHeight="1" spans="3:12">
+    <row r="97" customHeight="1" spans="3:14">
       <c r="C97" s="1">
         <v>96</v>
       </c>
@@ -4521,6 +4577,616 @@
         <v>20</v>
       </c>
       <c r="L97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:14">
+      <c r="E99" s="5"/>
+    </row>
+    <row r="100" customHeight="1" spans="3:14">
+      <c r="C100" s="1">
+        <v>100</v>
+      </c>
+      <c r="D100" s="1">
+        <v>9</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G100" s="2">
+        <v>100</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+      <c r="I100" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J100" s="1">
+        <v>1</v>
+      </c>
+      <c r="K100" s="1">
+        <v>10</v>
+      </c>
+      <c r="L100" s="1">
+        <v>100</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:14">
+      <c r="C101" s="1">
+        <v>101</v>
+      </c>
+      <c r="D101" s="1">
+        <v>9</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G101" s="2">
+        <v>100</v>
+      </c>
+      <c r="H101" s="1">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="1">
+        <v>10</v>
+      </c>
+      <c r="L101" s="1">
+        <v>100</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:14">
+      <c r="C102" s="1">
+        <v>102</v>
+      </c>
+      <c r="D102" s="1">
+        <v>9</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" s="1">
+        <v>50</v>
+      </c>
+      <c r="H102" s="1">
+        <v>50</v>
+      </c>
+      <c r="I102" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J102" s="1">
+        <v>10</v>
+      </c>
+      <c r="K102" s="1">
+        <v>20</v>
+      </c>
+      <c r="L102" s="1">
+        <v>4</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:14">
+      <c r="C103" s="1">
+        <v>103</v>
+      </c>
+      <c r="D103" s="1">
+        <v>9</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103" s="1">
+        <v>50</v>
+      </c>
+      <c r="H103" s="1">
+        <v>50</v>
+      </c>
+      <c r="I103" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J103" s="1">
+        <v>10</v>
+      </c>
+      <c r="K103" s="1">
+        <v>10</v>
+      </c>
+      <c r="L103" s="1">
+        <v>4</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N103" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C104" s="1">
+        <v>104</v>
+      </c>
+      <c r="D104" s="2">
+        <v>9</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G104" s="2">
+        <v>50</v>
+      </c>
+      <c r="H104" s="2">
+        <v>1</v>
+      </c>
+      <c r="I104" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J104" s="2">
+        <v>1</v>
+      </c>
+      <c r="K104" s="2">
+        <v>50</v>
+      </c>
+      <c r="L104" s="2">
+        <v>3</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N104" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C105" s="1">
+        <v>105</v>
+      </c>
+      <c r="D105" s="2">
+        <v>9</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G105" s="2">
+        <v>50</v>
+      </c>
+      <c r="H105" s="2">
+        <v>1</v>
+      </c>
+      <c r="I105" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J105" s="2">
+        <v>1</v>
+      </c>
+      <c r="K105" s="2">
+        <v>50</v>
+      </c>
+      <c r="L105" s="2">
+        <v>3</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N105" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C106" s="1">
+        <v>106</v>
+      </c>
+      <c r="D106" s="2">
+        <v>9</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G106" s="2">
+        <v>50</v>
+      </c>
+      <c r="H106" s="2">
+        <v>1</v>
+      </c>
+      <c r="I106" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J106" s="2">
+        <v>1</v>
+      </c>
+      <c r="K106" s="2">
+        <v>50</v>
+      </c>
+      <c r="L106" s="2">
+        <v>3</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N106" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C107" s="1">
+        <v>107</v>
+      </c>
+      <c r="D107" s="2">
+        <v>9</v>
+      </c>
+      <c r="E107" s="8">
+        <v>180017</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" s="2">
+        <v>50000</v>
+      </c>
+      <c r="H107" s="2">
+        <v>1</v>
+      </c>
+      <c r="I107" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J107" s="2">
+        <v>100</v>
+      </c>
+      <c r="K107" s="2">
+        <v>1</v>
+      </c>
+      <c r="L107" s="2">
+        <v>1</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C108" s="1">
+        <v>108</v>
+      </c>
+      <c r="D108" s="2">
+        <v>9</v>
+      </c>
+      <c r="E108" s="8">
+        <v>180018</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G108" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H108" s="2">
+        <v>1</v>
+      </c>
+      <c r="I108" s="2">
+        <v>10000</v>
+      </c>
+      <c r="J108" s="2">
+        <v>100</v>
+      </c>
+      <c r="K108" s="2">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2">
+        <v>1</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C109" s="1">
+        <v>109</v>
+      </c>
+      <c r="D109" s="2">
+        <v>9</v>
+      </c>
+      <c r="E109" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G109" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H109" s="2">
+        <v>99</v>
+      </c>
+      <c r="I109" s="2">
+        <v>99</v>
+      </c>
+      <c r="J109" s="2">
+        <v>100</v>
+      </c>
+      <c r="K109" s="2">
+        <v>2</v>
+      </c>
+      <c r="L109" s="2">
+        <v>2</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C110" s="1">
+        <v>110</v>
+      </c>
+      <c r="D110" s="2">
+        <v>9</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G110" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H110" s="2">
+        <v>99</v>
+      </c>
+      <c r="I110" s="2">
+        <v>99</v>
+      </c>
+      <c r="J110" s="2">
+        <v>100</v>
+      </c>
+      <c r="K110" s="2">
+        <v>2</v>
+      </c>
+      <c r="L110" s="2">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C111" s="1">
+        <v>111</v>
+      </c>
+      <c r="D111" s="2">
+        <v>9</v>
+      </c>
+      <c r="E111" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G111" s="2">
+        <v>3</v>
+      </c>
+      <c r="H111" s="2">
+        <v>70</v>
+      </c>
+      <c r="I111" s="2">
+        <v>99</v>
+      </c>
+      <c r="J111" s="2">
+        <v>3</v>
+      </c>
+      <c r="K111" s="2">
+        <v>2</v>
+      </c>
+      <c r="L111" s="2">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C112" s="1">
+        <v>112</v>
+      </c>
+      <c r="D112" s="2">
+        <v>9</v>
+      </c>
+      <c r="E112" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G112" s="2">
+        <v>3</v>
+      </c>
+      <c r="H112" s="2">
+        <v>10</v>
+      </c>
+      <c r="I112" s="2">
+        <v>98</v>
+      </c>
+      <c r="J112" s="2">
+        <v>1</v>
+      </c>
+      <c r="K112" s="2">
+        <v>10</v>
+      </c>
+      <c r="L112" s="2">
+        <v>1</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C113" s="1">
+        <v>113</v>
+      </c>
+      <c r="D113" s="2">
+        <v>9</v>
+      </c>
+      <c r="E113" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G113" s="2">
+        <v>100</v>
+      </c>
+      <c r="H113" s="2">
+        <v>1</v>
+      </c>
+      <c r="I113" s="2">
+        <v>98</v>
+      </c>
+      <c r="J113" s="2">
+        <v>1</v>
+      </c>
+      <c r="K113" s="2">
+        <v>80</v>
+      </c>
+      <c r="L113" s="2">
+        <v>3</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="114" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C114" s="1">
+        <v>114</v>
+      </c>
+      <c r="D114" s="2">
+        <v>9</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G114" s="2">
+        <v>10</v>
+      </c>
+      <c r="H114" s="2">
+        <v>70</v>
+      </c>
+      <c r="I114" s="2">
+        <v>100</v>
+      </c>
+      <c r="J114" s="2">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>5</v>
+      </c>
+      <c r="L114" s="2">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C115" s="1">
+        <v>115</v>
+      </c>
+      <c r="D115" s="2">
+        <v>9</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G115" s="2">
+        <v>8</v>
+      </c>
+      <c r="H115" s="2">
+        <v>95</v>
+      </c>
+      <c r="I115" s="2">
+        <v>100</v>
+      </c>
+      <c r="J115" s="2">
+        <v>1</v>
+      </c>
+      <c r="K115" s="2">
+        <v>2</v>
+      </c>
+      <c r="L115" s="2">
+        <v>1</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C116" s="1">
+        <v>116</v>
+      </c>
+      <c r="D116" s="2">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2">
+        <v>602</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G116" s="2">
+        <v>12</v>
+      </c>
+      <c r="H116" s="2">
+        <v>1</v>
+      </c>
+      <c r="I116" s="2">
+        <v>100</v>
+      </c>
+      <c r="J116" s="2">
+        <v>1</v>
+      </c>
+      <c r="K116" s="2">
+        <v>50</v>
+      </c>
+      <c r="L116" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Excel/DefendDropConfig.xlsx
+++ b/Excel/DefendDropConfig.xlsx
@@ -4608,8 +4608,8 @@
       <c r="J100" s="1">
         <v>1</v>
       </c>
-      <c r="K100" s="1">
-        <v>10</v>
+      <c r="K100" s="2">
+        <v>50</v>
       </c>
       <c r="L100" s="1">
         <v>100</v>
@@ -4643,8 +4643,8 @@
       <c r="J101" s="1">
         <v>1</v>
       </c>
-      <c r="K101" s="1">
-        <v>10</v>
+      <c r="K101" s="2">
+        <v>50</v>
       </c>
       <c r="L101" s="1">
         <v>100</v>
@@ -4670,7 +4670,7 @@
         <v>50</v>
       </c>
       <c r="H102" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I102" s="1">
         <v>10000</v>
@@ -4678,8 +4678,8 @@
       <c r="J102" s="1">
         <v>10</v>
       </c>
-      <c r="K102" s="1">
-        <v>20</v>
+      <c r="K102" s="2">
+        <v>50</v>
       </c>
       <c r="L102" s="1">
         <v>4</v>
@@ -4708,7 +4708,7 @@
         <v>50</v>
       </c>
       <c r="H103" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I103" s="1">
         <v>10000</v>
@@ -4716,8 +4716,8 @@
       <c r="J103" s="1">
         <v>10</v>
       </c>
-      <c r="K103" s="1">
-        <v>10</v>
+      <c r="K103" s="2">
+        <v>50</v>
       </c>
       <c r="L103" s="1">
         <v>4</v>
@@ -4745,7 +4745,7 @@
       <c r="G104" s="2">
         <v>50</v>
       </c>
-      <c r="H104" s="2">
+      <c r="H104" s="1">
         <v>1</v>
       </c>
       <c r="I104" s="2">
@@ -4783,7 +4783,7 @@
       <c r="G105" s="2">
         <v>50</v>
       </c>
-      <c r="H105" s="2">
+      <c r="H105" s="1">
         <v>1</v>
       </c>
       <c r="I105" s="2">
@@ -4821,7 +4821,7 @@
       <c r="G106" s="2">
         <v>50</v>
       </c>
-      <c r="H106" s="2">
+      <c r="H106" s="1">
         <v>1</v>
       </c>
       <c r="I106" s="2">
@@ -4859,7 +4859,7 @@
       <c r="G107" s="2">
         <v>50000</v>
       </c>
-      <c r="H107" s="2">
+      <c r="H107" s="1">
         <v>1</v>
       </c>
       <c r="I107" s="2">
@@ -4894,7 +4894,7 @@
       <c r="G108" s="2">
         <v>5000</v>
       </c>
-      <c r="H108" s="2">
+      <c r="H108" s="1">
         <v>1</v>
       </c>
       <c r="I108" s="2">
